--- a/project_task.xlsx
+++ b/project_task.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\front-end\buoi_22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Study\front-end\buoi_22\bc94_capstone_javascript_tai_tuyen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E306ED1C-4A8C-4E05-B6FB-0541B8E46FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4DA95F-DF12-42F7-8A28-32B94E343D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="40">
   <si>
     <t>Tasks Name</t>
   </si>
@@ -69,6 +69,99 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>14/06</t>
+  </si>
+  <si>
+    <t>Tai</t>
+  </si>
+  <si>
+    <t>16/06</t>
+  </si>
+  <si>
+    <t>getId(), showListProduct(),renderUI()</t>
+  </si>
+  <si>
+    <t>17/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">renderTotalPriceItem(), handleQuickView(), </t>
+  </si>
+  <si>
+    <t>17/07</t>
+  </si>
+  <si>
+    <t>19/06</t>
+  </si>
+  <si>
+    <t>clearCart, setLocalStorage(), getLocalStorage()</t>
+  </si>
+  <si>
+    <t>20/06</t>
+  </si>
+  <si>
+    <t>25/06</t>
+  </si>
+  <si>
+    <t>Controller, Model main.js, class product, productManage</t>
+  </si>
+  <si>
+    <t>Thiết lập các lớp chức năng:</t>
+  </si>
+  <si>
+    <t>Tuyen</t>
+  </si>
+  <si>
+    <t>Design giao diện Admin</t>
+  </si>
+  <si>
+    <t>Design giao diện Home, Store Client</t>
+  </si>
+  <si>
+    <t>18/06</t>
+  </si>
+  <si>
+    <t>21/06</t>
+  </si>
+  <si>
+    <t>class API services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">getListProductAPI(), addProduct(), delProduct(), editProduct(), getProductById(), </t>
+  </si>
+  <si>
+    <t>22/06</t>
+  </si>
+  <si>
+    <t>getID(), getInputProduct(), renderListProduct(), renderUI()</t>
+  </si>
+  <si>
+    <t>23/06</t>
+  </si>
+  <si>
+    <t>handleAdd(), handleDelete(), handleModalEdit(), handleEdit()</t>
+  </si>
+  <si>
+    <t>filterNameProduct(), sortItem(value, data)</t>
+  </si>
+  <si>
+    <t>validation input</t>
+  </si>
+  <si>
+    <t>26/06</t>
+  </si>
+  <si>
+    <t>27/06</t>
+  </si>
+  <si>
+    <t>28/06</t>
+  </si>
+  <si>
+    <t>27/07</t>
+  </si>
+  <si>
+    <t>handleDeleteItemCart(), handleAddCart(), renderCountItemCart(), function handleDescCountItem(), handleIncrCountItem()</t>
   </si>
 </sst>
 </file>
@@ -78,7 +171,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,16 +195,109 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
+      <color theme="0"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -144,12 +330,78 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAEABAB"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor rgb="FFAEABAB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor rgb="FFAEABAB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor rgb="FFAEABAB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor rgb="FFAEABAB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -249,22 +501,72 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -275,70 +577,147 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="13" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="13" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="18" fillId="16" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6EFCE"/>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -567,7 +946,7 @@
   <dimension ref="A1:J986"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" outlineLevelRow="2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.5" style="7" customWidth="1"/>
+    <col min="1" max="1" width="25.25" style="4" customWidth="1"/>
     <col min="2" max="4" width="7.625" customWidth="1"/>
     <col min="5" max="5" width="10.25" customWidth="1"/>
     <col min="6" max="6" width="7.625" customWidth="1"/>
@@ -579,7 +958,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -606,184 +985,468 @@
       <c r="I1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:10" s="7" customFormat="1" ht="21.75" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="18"/>
+    <row r="2" spans="1:10" s="48" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="46">
+        <v>1</v>
+      </c>
+      <c r="E2" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="46">
+        <v>1</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="47"/>
     </row>
-    <row r="3" spans="1:10" s="7" customFormat="1" ht="14.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="18"/>
+    <row r="3" spans="1:10" s="21" customFormat="1" ht="26.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" s="20"/>
     </row>
-    <row r="4" spans="1:10" s="7" customFormat="1" ht="14.25" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="18"/>
+    <row r="4" spans="1:10" s="26" customFormat="1" ht="33.75" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="23">
+        <v>1</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="23">
+        <v>1</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="25"/>
     </row>
-    <row r="5" spans="1:10" s="7" customFormat="1" ht="14.25" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="18"/>
+    <row r="5" spans="1:10" s="11" customFormat="1" ht="25.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A5" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" s="8">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="10"/>
     </row>
-    <row r="6" spans="1:10" s="7" customFormat="1" ht="14.25" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="18"/>
+    <row r="6" spans="1:10" s="11" customFormat="1" ht="28.5" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:10" s="7" customFormat="1" ht="9" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="19"/>
+    <row r="7" spans="1:10" s="11" customFormat="1" ht="60.75" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.2">
+      <c r="A7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="8">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="13"/>
     </row>
-    <row r="8" spans="1:10" s="7" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="18"/>
+    <row r="8" spans="1:10" s="11" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="8">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="10"/>
     </row>
-    <row r="9" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="18"/>
+    <row r="9" spans="1:10" s="39" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="40"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="41"/>
     </row>
-    <row r="10" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="18"/>
+    <row r="10" spans="1:10" s="48" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="44">
+        <v>1</v>
+      </c>
+      <c r="E10" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="46">
+        <v>1</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="47"/>
     </row>
-    <row r="11" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="18"/>
+    <row r="11" spans="1:10" s="21" customFormat="1" ht="26.25" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="17"/>
+      <c r="C11" s="17"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="20"/>
     </row>
-    <row r="12" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="11"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="18"/>
+    <row r="12" spans="1:10" s="35" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="28">
+        <v>1</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="23">
+        <v>1</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="34"/>
     </row>
-    <row r="13" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="11"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="18"/>
+    <row r="13" spans="1:10" s="26" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="32">
+        <v>1</v>
+      </c>
+      <c r="E13" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="31" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="33">
+        <v>1</v>
+      </c>
+      <c r="I13" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="25"/>
     </row>
-    <row r="14" spans="1:10" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="11"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="18"/>
+    <row r="14" spans="1:10" s="35" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="28">
+        <v>1</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="23">
+        <v>1</v>
+      </c>
+      <c r="I14" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="34"/>
     </row>
-    <row r="15" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:10" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="32">
+        <v>1</v>
+      </c>
+      <c r="E15" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="33">
+        <v>1</v>
+      </c>
+      <c r="I15" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" spans="1:10" s="36" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="32">
+        <v>1</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="33">
+        <v>1</v>
+      </c>
+      <c r="I16" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="34"/>
+    </row>
+    <row r="17" spans="1:10" s="36" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="32">
+        <v>1</v>
+      </c>
+      <c r="E17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="33">
+        <v>1</v>
+      </c>
+      <c r="I17" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="34"/>
+    </row>
+    <row r="18" spans="1:10" s="36" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="32">
+        <v>1</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="33">
+        <v>1</v>
+      </c>
+      <c r="I18" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="34"/>
+    </row>
+    <row r="19" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -1739,13 +2402,12 @@
     <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <conditionalFormatting sqref="D2 D4:D14">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
-      <formula>0.99</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2 H4:H14">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+  <mergeCells count="1">
+    <mergeCell ref="A9:XFD9"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <conditionalFormatting sqref="D2:D8 H2:H8 H10:H18 D10:D18">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0.99</formula>
     </cfRule>
   </conditionalFormatting>
